--- a/data/trans_camb/IP16A98-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 26,76</t>
+          <t>-8,37; 27,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 28,48</t>
+          <t>-6,3; 28,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 18,97</t>
+          <t>-15,81; 19,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 27,54</t>
+          <t>-13,41; 26,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 17,68</t>
+          <t>-7,84; 16,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 20,76</t>
+          <t>-4,99; 21,44</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 361,43</t>
+          <t>-42,61; 349,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 377,53</t>
+          <t>-31,84; 347,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,63; 192,86</t>
+          <t>-69,5; 191,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 285,64</t>
+          <t>-58,19; 286,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 149,52</t>
+          <t>-37,81; 153,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 178,07</t>
+          <t>-25,22; 187,9</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 19,22</t>
+          <t>-10,89; 18,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 37,91</t>
+          <t>-11,57; 37,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 26,75</t>
+          <t>0,35; 27,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 13,67</t>
+          <t>-8,4; 13,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 19,46</t>
+          <t>-1,48; 17,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 18,3</t>
+          <t>-6,16; 19,12</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,04; 176,38</t>
+          <t>-41,09; 173,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 405,96</t>
+          <t>-57,6; 385,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 444,5</t>
+          <t>-4,67; 483,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 245,47</t>
+          <t>-49,86; 240,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 177,88</t>
+          <t>-10,39; 161,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 166,94</t>
+          <t>-34,33; 196,88</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 11,74</t>
+          <t>-7,69; 11,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 20,08</t>
+          <t>-6,78; 20,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 23,04</t>
+          <t>-5,59; 23,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 24,87</t>
+          <t>-4,94; 27,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 13,92</t>
+          <t>-3,32; 14,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 18,76</t>
+          <t>-2,23; 18,43</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 930,1</t>
+          <t>-55,63; 894,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 505,39</t>
+          <t>-52,01; 519,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,22; 592,84</t>
+          <t>-49,11; 853,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 358,33</t>
+          <t>-33,31; 382,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 416,14</t>
+          <t>-24,84; 413,77</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 16,23</t>
+          <t>-7,56; 17,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 21,03</t>
+          <t>-4,24; 21,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 12,56</t>
+          <t>-17,39; 12,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 21,62</t>
+          <t>-10,68; 20,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 9,64</t>
+          <t>-9,49; 9,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 15,18</t>
+          <t>-5,37; 16,01</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 483,72</t>
+          <t>-65,49; 544,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 527,31</t>
+          <t>-35,47; 780,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,95; 109,12</t>
+          <t>-67,52; 93,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 163,67</t>
+          <t>-40,69; 138,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,79; 97,37</t>
+          <t>-51,71; 90,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 145,57</t>
+          <t>-29,69; 137,81</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 11,83</t>
+          <t>-0,93; 12,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 15,75</t>
+          <t>-2,44; 16,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 13,49</t>
+          <t>-2,54; 12,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 11,53</t>
+          <t>-4,58; 10,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 10,12</t>
+          <t>-0,1; 10,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,9</t>
+          <t>-1,95; 10,57</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 132,68</t>
+          <t>-7,41; 143,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 167,95</t>
+          <t>-18,97; 175,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 121,69</t>
+          <t>-14,46; 109,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 99,37</t>
+          <t>-24,46; 87,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,52; 87,15</t>
+          <t>-0,24; 89,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 92,75</t>
+          <t>-10,18; 87,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 27,25</t>
+          <t>-9,99; 27,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 28,98</t>
+          <t>-6,01; 27,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 19,6</t>
+          <t>-17,5; 17,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 26,41</t>
+          <t>-14,2; 27,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 16,88</t>
+          <t>-7,47; 18,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 21,44</t>
+          <t>-5,41; 20,4</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 349,6</t>
+          <t>-46,83; 310,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,84; 347,07</t>
+          <t>-30,48; 429,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,5; 191,64</t>
+          <t>-68,19; 191,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,19; 286,01</t>
+          <t>-67,15; 258,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 153,05</t>
+          <t>-35,71; 161,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 187,9</t>
+          <t>-28,21; 175,62</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 18,83</t>
+          <t>-9,65; 18,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 37,68</t>
+          <t>-11,38; 34,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 27,2</t>
+          <t>-0,32; 26,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 13,94</t>
+          <t>-8,31; 14,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 17,95</t>
+          <t>-0,6; 18,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 19,12</t>
+          <t>-5,87; 20,74</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 173,63</t>
+          <t>-38,81; 168,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,6; 385,73</t>
+          <t>-57,23; 294,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 483,39</t>
+          <t>-9,09; 453,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 240,42</t>
+          <t>-44,65; 252,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 161,11</t>
+          <t>-4,86; 180,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 196,88</t>
+          <t>-36,75; 179,76</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 11,77</t>
+          <t>-8,04; 11,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 20,07</t>
+          <t>-6,69; 20,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 23,02</t>
+          <t>-4,05; 24,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 27,68</t>
+          <t>-5,37; 27,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 14,38</t>
+          <t>-3,33; 13,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 18,43</t>
+          <t>-2,28; 18,78</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,63; 894,18</t>
+          <t>-45,56; 1085,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,01; 519,12</t>
+          <t>-40,71; 563,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 853,45</t>
+          <t>-58,2; 664,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 382,58</t>
+          <t>-39,25; 312,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 413,77</t>
+          <t>-24,55; 386,01</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 17,22</t>
+          <t>-7,18; 17,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 21,76</t>
+          <t>-3,81; 21,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 12,74</t>
+          <t>-19,42; 12,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 20,97</t>
+          <t>-11,69; 20,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 9,63</t>
+          <t>-9,39; 10,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 16,01</t>
+          <t>-4,2; 16,35</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 544,08</t>
+          <t>-64,17; 409,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 780,89</t>
+          <t>-43,77; 583,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,52; 93,18</t>
+          <t>-70,99; 91,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 138,47</t>
+          <t>-44,33; 162,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,71; 90,0</t>
+          <t>-50,57; 103,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 137,81</t>
+          <t>-22,39; 159,41</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 12,88</t>
+          <t>-1,63; 12,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 16,88</t>
+          <t>-2,55; 15,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 12,61</t>
+          <t>-2,05; 13,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 10,36</t>
+          <t>-3,81; 11,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 10,03</t>
+          <t>-0,4; 10,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 10,57</t>
+          <t>-1,22; 10,97</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 143,36</t>
+          <t>-11,62; 132,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 175,55</t>
+          <t>-19,55; 155,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 109,24</t>
+          <t>-12,69; 108,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 87,97</t>
+          <t>-20,72; 102,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 89,39</t>
+          <t>-3,15; 86,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 87,63</t>
+          <t>-7,33; 97,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Habitat-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>8,07</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,94</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>9,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>6,68</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 27,87</t>
+          <t>-14,81; 18,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 27,93</t>
+          <t>-13,28; 27,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 17,82</t>
+          <t>-9,96; 26,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 27,49</t>
+          <t>-7,22; 27,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 18,1</t>
+          <t>-8,46; 17,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 20,4</t>
+          <t>-5,77; 20,51</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23,29%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>52,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>64,39%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 310,79</t>
+          <t>-65,63; 192,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 429,73</t>
+          <t>-65,19; 271,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,19; 191,93</t>
+          <t>-47,81; 361,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,15; 258,45</t>
+          <t>-39,47; 374,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,71; 161,05</t>
+          <t>-40,38; 149,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 175,62</t>
+          <t>-29,09; 170,04</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>4,82</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,14</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,9</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>-0,66</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 18,18</t>
+          <t>-2,02; 26,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 34,98</t>
+          <t>-9,33; 12,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 26,71</t>
+          <t>-11,04; 19,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 14,43</t>
+          <t>-15,4; 11,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 18,41</t>
+          <t>-1,29; 19,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 20,74</t>
+          <t>-9,51; 7,31</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>108,91%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,38%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>26,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>108,91%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>-17,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>-4,37%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,81; 168,05</t>
+          <t>-16,86; 444,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 294,29</t>
+          <t>-52,83; 228,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 453,79</t>
+          <t>-45,04; 176,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 252,96</t>
+          <t>-67,48; 102,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 180,21</t>
+          <t>-9,01; 177,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,75; 179,76</t>
+          <t>-47,37; 69,06</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,84</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>1,06</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8,23</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,9</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,14</t>
+          <t>15,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,44</t>
+          <t>11,58</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 11,35</t>
+          <t>-4,76; 23,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 20,47</t>
+          <t>-5,04; 26,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 24,31</t>
+          <t>-8,95; 11,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 27,18</t>
+          <t>5,11; 27,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 13,91</t>
+          <t>-3,49; 13,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 18,78</t>
+          <t>2,68; 23,42</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>93,74%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82,62%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>18,35%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>142,93%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>268,91%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>150,93%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-44,66; 505,39</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-55,69; 682,16</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-45,56; 1085,39</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-40,71; 563,18</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 664,44</t>
+          <t>19,15; 1422,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 312,61</t>
+          <t>-33,49; 358,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 386,01</t>
+          <t>13,53; 667,86</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>4,06</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>8,35</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>6,34</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 17,03</t>
+          <t>-18,25; 12,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 21,75</t>
+          <t>-11,07; 22,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 12,21</t>
+          <t>-7,77; 16,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 20,55</t>
+          <t>-3,35; 22,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 10,81</t>
+          <t>-10,19; 9,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 16,35</t>
+          <t>-4,73; 16,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-16,33%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23,03%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>47,5%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-16,33%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 409,06</t>
+          <t>-68,95; 109,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 583,55</t>
+          <t>-42,48; 172,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,99; 91,84</t>
+          <t>-62,41; 483,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 162,85</t>
+          <t>-36,36; 546,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,57; 103,49</t>
+          <t>-54,79; 97,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 159,41</t>
+          <t>-28,2; 154,4</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>4,92</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>7,37</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>5,18</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 12,02</t>
+          <t>-2,63; 13,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 15,77</t>
+          <t>-4,24; 12,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 13,37</t>
+          <t>-1,99; 11,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 11,73</t>
+          <t>0,18; 14,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 10,16</t>
+          <t>-0,06; 10,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 10,97</t>
+          <t>0,35; 10,25</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33,76%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20,91%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>40,69%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>52,49%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 132,4</t>
+          <t>-14,01; 121,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 155,84</t>
+          <t>-25,18; 102,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 108,96</t>
+          <t>-13,87; 132,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 102,43</t>
+          <t>-0,41; 162,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 86,3</t>
+          <t>1,52; 87,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 97,83</t>
+          <t>2,87; 89,77</t>
         </is>
       </c>
     </row>
